--- a/z0bug_odoo/z0bug_odoo/testenv/account_rc_type.xlsx
+++ b/z0bug_odoo/z0bug_odoo/testenv/account_rc_type.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -28,31 +28,13 @@
     <t xml:space="preserve">name</t>
   </si>
   <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">company_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">method</t>
-  </si>
-  <si>
-    <t xml:space="preserve">partner_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">with_supplier_self_invoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">partner_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">journal_id</t>
+    <t xml:space="preserve">self_journal_id</t>
   </si>
   <si>
     <t xml:space="preserve">payment_journal_id</t>
   </si>
   <si>
-    <t xml:space="preserve">transitory_account_id</t>
+    <t xml:space="preserve">transient_account_id</t>
   </si>
   <si>
     <t xml:space="preserve">l10n_it_reverse_charge.account_rc_type_1</t>
@@ -61,18 +43,6 @@
     <t xml:space="preserve">Reverse charge locale</t>
   </si>
   <si>
-    <t xml:space="preserve">Usare per RC locale (italia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">selfinvoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">supplier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z0bug.partner_mycompany</t>
-  </si>
-  <si>
     <t xml:space="preserve">external.INV</t>
   </si>
   <si>
@@ -85,22 +55,13 @@
     <t xml:space="preserve">l10n_it_reverse_charge.account_rc_type_2</t>
   </si>
   <si>
+    <t xml:space="preserve">Reverse charge Extra-EU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l10n_it_reverse_charge.account_rc_type_3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reverse charge EU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usare per RC interna EU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">l10n_it_reverse_charge.account_rc_type_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reverse charge Extra-EU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usare per RC estero no EU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">other</t>
   </si>
 </sst>
 </file>
@@ -182,12 +143,8 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -208,23 +165,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -339,154 +279,86 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="11.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="11.76953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="23.38"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="19.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1016" style="1" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.27"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1006" min="6" style="1" width="11.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="1007" style="1" width="11.52"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="1024" style="1" width="11.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>12</v>
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>21</v>
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>24</v>
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
